--- a/poll_averages.xlsx
+++ b/poll_averages.xlsx
@@ -522,7 +522,7 @@
         <v>0.295</v>
       </c>
       <c r="J2" t="n">
-        <v>0.125</v>
+        <v>0.115</v>
       </c>
       <c r="K2" t="n">
         <v>0.5600000000000001</v>
